--- a/TruScore logic/CARE Pillar.xlsx
+++ b/TruScore logic/CARE Pillar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TrueScan-FoodScanner\TruScore logic\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4A9C9787-C2DB-4EEA-AEB6-080384086808}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D6C61F-1490-427E-9FAE-53A084645FFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{02E5C598-28FB-4408-834F-85B092D67E19}"/>
   </bookViews>
@@ -60,9 +60,6 @@
     <t xml:space="preserve"> Base Score </t>
   </si>
   <si>
-    <t xml:space="preserve"> Slightly positive neutral; assumes ethical until violations </t>
-  </si>
-  <si>
     <t xml:space="preserve"> Internal Logic (No external source) </t>
   </si>
   <si>
@@ -75,121 +72,124 @@
     <t xml:space="preserve"> 15 (uniform) </t>
   </si>
   <si>
-    <t xml:space="preserve"> Uniform 15 consistency; HSUS defends without negativity. Ditched geo-weight for MVP simplicity\'97embed rewards in certs/violations. </t>
-  </si>
-  <si>
     <t xml:space="preserve"> 1. Always starting point; adjustments added/subtracted. </t>
   </si>
   <si>
     <t xml:space="preserve"> Certifications </t>
   </si>
   <si>
-    <t xml:space="preserve"> Strong certs; fair/animal welfare </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Fairtrade, RSPO, MSC/ASC, RSPCA, Organic (EU/US/CA/AU), Leaping Bunny, B Corp &gt; Country/Global OFF </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Welfare boycotts (30% X virality 2025) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> labels_tags (array filtered) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Fairtrade=+8, Organic=+7, Rainforest/UTZ=+6, MSC/ASC=+6 (sustainable fishing), RSPCA/Leaping Bunny/B Corp=+5, Cage-Free/Free-Range=+4 (animal farming/slaughter) (stack cap +15) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Tiered by impact breadth (holistic high, specific low); studies defend (e.g., Fairtrade 20% poverty cut). Embedded geo-reward here\'97no base complexity. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1. Local govt certs (e.g., USDA Organic US) &gt; 2. Country OFF &gt; 3. Global OFF; bonus if match; +6 MSC/ASC for fishing, +4 cage-free for farming/slaughter. </t>
-  </si>
-  <si>
     <t xml:space="preserve"> Animal Cruelty </t>
   </si>
   <si>
     <t xml:space="preserve"> No animal cruelty </t>
   </si>
   <si>
-    <t xml:space="preserve"> PETA, HSUS, RSPCA &gt; Country/Global OFF + X/Reuters for news tie </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Animal scandals (50% disgust X 2025) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> brands_tags (cruelty filter), violations API, x_semantic_score/news mentions (&gt;10k last 6mo) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Major=-15 (e.g., factory farming/slaughter/cruelty/news tie), minor=-5; brand/parent high-impact=-3 overlay. Dedup if news relevance &gt;80% (net -5). </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> PETA/HSUS/RSPCA scorecards defend; geo local overrides. Embed sentiment/news here\'97dedup to avoid double-penalty. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1. PETA/HSUS/RSPCA &gt; 2. Country OFF &gt; 3. Global OFF; deduct if cruelty match/news tie; overlay brand/parent if low. X/Reuters embed for relevance. </t>
-  </si>
-  <si>
     <t xml:space="preserve"> Labor Violations/Human Exploitation </t>
   </si>
   <si>
-    <t xml:space="preserve"> No labor/human exploitation </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DOL (US), Buycott, Open Corporates &gt; Country/Global OFF + X/Reuters for news tie </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Labor scandals (30% distrust X 2025) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> brands_tags (labor filter), violations API, x_semantic_score/news mentions (&gt;10k last 6mo) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Minor=-5 (e.g., under-pay/over-work/min breaks/unpaid overtime/anti-competitive/predatory/bullying/news tie), major=-15 (e.g., child labor/slavery); brand/parent high-impact=-3 overlay. Dedup if news relevance &gt;80% (net -5). </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DOL/Buycott/Open Corporates defend; geo local overrides. Embed sentiment/news here\'97dedup to avoid double-penalty. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1. DOL/Buycott/Open Corporates &gt; 2. Country OFF &gt; 3. Global OFF; deduct if labor match/news tie; overlay brand/parent if low. X/Reuters embed for relevance. </t>
-  </si>
-  <si>
     <t xml:space="preserve"> Recalls </t>
   </si>
   <si>
     <t xml:space="preserve"> No safety recalls </t>
   </si>
   <si>
-    <t xml:space="preserve"> FDA (US recalls), CFIA (CA), FSANZ (AU/NZ), UK FSA/EFSA, MHLW (Japan), CFS (HK), SFA (SG) &gt; Buycott &gt; Country/Global OFF + X/Reuters for news tie </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 15-25% virality (X spikes on Nestle 2025) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> recalls API, x_semantic_score/news mentions (&gt;10k last 6mo) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> -10 (temp if within last 12mo/news tie, universal); brand/parent high-impact=-3 overlay if recall history </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Boycott studies defend; 12mo bound prevents perpetual harshness per sentiment fade. Universal penalties\'97recall in one location = global deduct (poor care distrib-wide). Embed sentiment/news here\'97dedup if relevance &gt;80% (net -10). </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1. Local govt recalls (e.g., FDA/CFIA/FSANZ) &gt; 2. Buycott &gt; 3. Country OFF &gt; 4. Global OFF &gt; 5. User subs if gaps; deduct if flag/news tie and within 12mo (universal); overlay brand/parent if low. X/Reuters embed for relevance. </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Overall Pillar Cap </t>
-  </si>
-  <si>
     <t xml:space="preserve"> Allows wake-up viral on zero scores for bad deducts </t>
   </si>
   <si>
     <t xml:space="preserve"> Min 0 (floor after all adjustments) </t>
   </si>
   <si>
-    <t xml:space="preserve"> Caps final Care score at min 0; zero "unethical" callout on junk\'97viral boycott rage. </t>
-  </si>
-  <si>
     <t xml:space="preserve"> 1. Applied after all adjustments; overrides if &lt;0. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Slightly positive neutral; assumes ethical till violations </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Uniform 15 consistency; HSUS defends without negativity; fair to indies avoids X backlash on bias. No data = neutral, prompt user subs for gaps. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ethical certifications; fair treatment </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fairtrade Intl, ACO (AU), USDA Organic, EU Organic (EFSA), IFOAM, Rainforest Alliance, UTZ, MSC/ASC/Ocean Wise/Friend of the Sea, RSPCA/Leaping Bunny/B Corp, GlobalG.A.P, Cage-Free, Free-Range, Free-Roaming &gt; labels_tags array filtered (stack cap +15) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 40% virality (X spikes on Fairtrade 2025) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> labels_tags (array filtered for match) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Fairtrade=+8, Organic=+7, Rainforest/UTZ=+6, MSC/ASC=+6 (sustainable fishing), Ocean Wise=+5 (sustainable wild catch), Friend of the Sea=+4 (eco-aquaculture), RSPCA/Leaping Bunny/B Corp=+5, GlobalG.A.P=+4, Free-Roaming=+5, Free-Range=+3, Cage-Free=+1 (stack cap +15) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Boycott studies defend; virality on "Fairtrade Certified" shares. Stack cap prevents over-reward. Mandate embed here'97no base complexity. Exhaustive list covers G20 standards (e.g., EU Organic for geo). Fuzzy match &gt;80% on labels for variants. Geo certs apply universally (e.g., EFSA cert on EU product scanned in AU scores full points\'97reliance on any geography's practices for multi-national distribution). Tiered animal welfare (Cage-Free basic no-cages but misleading +1, Free-Range outdoor access but limited +3, Free-Roaming full mobility +5) and fishing (MSC/ASC base +6, Ocean Wise wild +5, Friend of the Sea eco +4) for nuanced ethics. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. Primary cert orgs (e.g., Fairtrade Intl/USDA/EFSA/IFOAM/GlobalG.A.P/RSPCA/MSC/Ocean Wise/Friend of the Sea) &gt; 2. Local govt certs (e.g., ACO AU) &gt; 3. Country OFF &gt; 4. Global OFF; stack bonuses cap +15; geo certs universal. User subs if no data. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PETA, Ethical Consumer, HSUS/RSPCA/ASPCA, Compassion in World Farming &gt; Buycott &gt; Country/Global OFF </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 50% virality (X spikes on factory farming 2025) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> brands_tags (cruelty filter), violations API </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Limited concerns=-4 (e.g., minor welfare lapses/BBFAW tier 5-6), moderate concerns=-8 (e.g., overcrowding/poor transport/BBFAW tier 3-4), major concerns=-15 (e.g., factory farming/slaughter/cruel testing/BBFAW tier 1-2); brand/parent assessed separately with same tiers (-4/-8/-15), mutually exclusive (no deduct if product hits) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Boycott studies defend; geo local overrides. Exhaustive sources for G20 coverage (added ASPCA for US). Fuzzy matching &gt;80% for better product/brand hits. Parent chaining via fuzzy matching (&gt;80% on brands_tags) and Oxfam CSVs/Open Corporates API for product &gt; brand &gt; parent (depth 3) to ensure accountability.  Severity from BBFAW tiers (tier 1-2 major, 3-4 moderate, 5-6 limited) for defensibility. No data = neutral, prompt subs. Negative news from X/Reuters applied as banner alert (scoring neutral)\'97"Recent cruelty buzz\'97check sources" to avoid rumor risks, keep time-bound &lt;12months. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. PETA/Ethical Consumer/HSUS/RSPCA/ASPCA/Compassion (BBFAW) &gt; 2. Buycott &gt; 3. Country OFF &gt; 4. Global OFF; deduct if match (fuzzy &gt;80%); . Time-bound &lt;12months X/Reuters banner for news tie. User subs if no data. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> No labor violations/exploitation </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DOL List of Goods (US child/forced labor), Walk Free Global Slavery Index, Oxfam Behind the Brands, ILO Labor Standards &gt; Buycott/Open Corporates &gt; Country/Global OFF </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 70% virality (X spikes on child labor cocoa 2025) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> brands_tags (labor filter), violations API </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Limited concerns=-4 (e.g., under-pay/over-work), moderate concerns=-8 (e.g., unsafe conditions), major=-15 (e.g., child labor/slavery); brand/parent assessed separately with same tiers (-4/-8/-15), mutually exclusive (no deduct if product hits) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Boycott studies defend; geo local overrides. Exhaustive list covers G20 (added ILO for global labor). Fuzzy match &gt;80% on labels for better product/brand hits. Parent chaining via fuzzy matching (&gt;80% on brands_tags) and Oxfam CSVs/Open Corporates API for product &gt; brand &gt; parent (depth 3) to ensure accountabilitySeverity from Walk Free/DOL (high-risk major, medium moderate, low limited) for defensibility. No data = neutral, prompt subs. Ties to geopolitics (e.g., palm labor in ID/MY). Negative news from X/Reuters as banner alert (scoring neutral)\'97"Labor concerns in news\'97verify" to sidestep rumors, keep time-bound &lt;12months. </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1. DOL/Walk Free/Oxfam/ILO &gt; 2. Buycott/Open Corporates &gt; 3. Country OFF &gt; 4. Global OFF; deduct if labor match (fuzzy &gt;80%); . Time-bound &lt;12months X/Reuters banner for news tie. User subs if no data. </t>
+  </si>
+  <si>
+    <t>FDA (US recalls), CFIA (CA), FSANZ (AU/NZ), EFSA/RASFF (EU) &gt; Country/Global OFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15-25% virality (X spikes on Nestle 2025) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> recalls API</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limited concerns=-4 (Class III/low risk), major=-15 (Class I/high risk), moderate=-8 (Class II/med risk) </t>
+  </si>
+  <si>
+    <t>Boycott studies defend; Universal penalties—recall in one location = global deduct (poor care distrib-wide). Semantic/news carved to banners only (e.g., "Potential Recall Buzz—Verify Sources" for shares; &gt;0.3 threshold triggers, no score hit to mitigate fake news, keep time-bound &lt;3months). Severity from FDA/class (Class I major, II moderate, III limited) for defensibility. No data = neutral, prompt subs</t>
+  </si>
+  <si>
+    <t>Country OFF &gt; 2. Global OFF &gt; 3. Local govt recalls (FDA/CFIA/FSANZ/EFSA/RASFF); deduct if flag within 3month (universal); &lt;3months time-bound for X/Reuters for banner ties only (no scoring).  User subs if no data. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overall Pillar Cap </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Caps final Care score at min 0; zero "unethical" callout on junk'97viral boycott rage. </t>
   </si>
 </sst>
 </file>
@@ -243,15 +243,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -576,11 +577,11 @@
     <col min="1" max="1" width="13.28515625" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" customWidth="1"/>
     <col min="3" max="3" width="23.5703125" customWidth="1"/>
-    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+    <col min="4" max="4" width="27.42578125" customWidth="1"/>
     <col min="5" max="5" width="25.7109375" customWidth="1"/>
     <col min="6" max="6" width="24.140625" customWidth="1"/>
     <col min="7" max="7" width="38.7109375" customWidth="1"/>
-    <col min="8" max="8" width="33.42578125" customWidth="1"/>
+    <col min="8" max="8" width="56.42578125" customWidth="1"/>
     <col min="9" max="9" width="31.42578125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -588,7 +589,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -614,167 +615,167 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="102" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="4" t="s">
+    </row>
+    <row r="3" spans="1:9" ht="207" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4"/>
+      <c r="B3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="C3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="183.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="3" t="s">
         <v>17</v>
       </c>
+      <c r="C4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>39</v>
+      </c>
     </row>
-    <row r="3" spans="1:9" ht="129" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="4" t="s">
+    <row r="5" spans="1:9" ht="208.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="87.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="134.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="H5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>41</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="173.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5"/>
+      <c r="A6" s="4"/>
       <c r="B6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>49</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
+      <c r="A7" s="4"/>
       <c r="B7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="H7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="C7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>54</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
